--- a/data_extactor/batch_10_fa/batch_0093_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0093_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نرم‌افزار پرونده الکترونیک سلامت Electronic medical record EMR | نرم‌افزار طراحی عینک | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار SAP</t>
+          <t>نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار طراحی عینک | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | درک مطلب خواندن</t>
+          <t>نظارت | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | ریاضیات | خدمات مشتریان و پرسنلی | امور اداری و مدیریت</t>
+          <t>تولید و فرآوری | مکانیک | ریاضیات | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات دست و بازو | چالاکی انگشتان | دقت کنترل | چالاکی دست | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | تجسم فضایی | ترتیب‌دهی به اطلاعات | تشخیص گفتار | تشخیص رنگ بصری | سرعت مچ و انگشت | زمان عکس‌العمل | کنترل نرخ | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | درک مطلب کتبی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت انگشتان | دقت کنترل | مهارت دستی | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات | تشخیص گفتار | تشخیص رنگ بصری | سرعت مچ و انگشتان | زمان عکس‌العمل | کنترل نرخ | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | درک کتبی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>داخل ساختمان، محیط کنترل‌شده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | سرعت تعیین‌شده توسط سرعت تجهیزات | صرف زمان به صورت ایستاده | قرار گرفتن در معرض آلاینده‌ها | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | نزدیکی فیزیکی</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | سرعت تعیین‌شده توسط سرعت تجهیزات | صرف زمان برای ایستادن | قرار گرفتن در معرض آلاینده‌ها | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکاران دوربین و تجهیزات عکاسی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | حکاکان و قلم‌زنان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و فرم‌دهی الیاف مصنوعی و شیشه‌ای | شیشه‌گران، قالب‌گیران، خم‌کنندگان و پرداخت‌کاران | کارگران سنگ‌زنی و صیقل‌کاری دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، صیقل‌کاری و پرداخت فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراشکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | قالب‌گیران، شکل‌دهندگان و ریخته‌گران به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندگانه فلز و پلاستیک | عینک‌سازان طبی، فروش و ساخت | تکنسین‌های فوتونیک | مونتاژکنندگان و تنظیم‌کنندگان ابزارهای زمان‌سنجی | تیزکنندگان و سنگ‌زنان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری نرم و سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری به جز اره‌کشی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکاران دوربین و تجهیزات عکاسی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | حکاکان و تیزاب‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | شیشه‌گران، قالب‌سازان، خم‌کاران و پرداخت‌کاران شیشه | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | عینک‌سازان، توزیع‌کننده | تکنسین‌های فوتونیک | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | امنیت و ایمنی عمومی | آموزش و پرورش | زبان انگلیسی | ریاضیات | خدمات مشتریان و پرسنلی</t>
+          <t>تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی | آموزش و پرورش | زبان انگلیسی | ریاضیات | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | بینایی نزدیک | دقت کنترل | چالاکی دست | سرعت ادراکی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری بستار | ترتیب‌دهی به اطلاعات | قدرت تنه | زمان عکس‌العمل | کنترل نرخ | هماهنگی چند عضو | چالاکی انگشتان | وضوح گفتار | تشخیص گفتار</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | دقت کنترل | مهارت دستی | سرعت ادراکی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | قدرت تنه | زمان عکس‌العمل | کنترل نرخ | هماهنگی چند عضو | مهارت انگشتان | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>سرعت تعیین‌شده توسط سرعت تجهیزات | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | سلامت و ایمنی سایر کارگران | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | داخل ساختمان، محیط کنترل‌شده | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوحی از نویز که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت تکرار وظایف یکسان | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای خم شدن یا چرخاندن بدن | صرف زمان برای راه رفتن یا دویدن | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری</t>
+          <t>سرعت تعیین‌شده توسط سرعت تجهیزات | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای راه رفتن یا دویدن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، سنگ‌زنی و صیقل‌کاری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و فرم‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، فرم‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان کوره، تنور، خشک‌کن و دیگ بخار | کارگران سنگ‌زنی و صیقل‌کاری دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، صیقل‌کاری و پرداخت فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران نگهداری و تعمیرات ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کن | قالب‌گیران، شکل‌دهندگان و ریخته‌گران به جز فلز و پلاستیک | بسته‌بندها و عدل‌بندهای دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | اپراتورها و متصدیان ماشین‌های رنگرزی و سفیدگری منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری به جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | بسته‌بندهای دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب خواندن | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات دست و بازو | تشخیص رنگ بصری | چالاکی دست | چالاکی انگشتان | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | تشخیص رنگ بصری | مهارت دستی | مهارت انگشتان | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوحی از نویز که حواس‌پرت‌کننده یا آزاردهنده هستند | ارتباط با دیگران | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | برش‌کاران و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | حکاکان و قلم‌زنان | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و صیقل‌کاری دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، صیقل‌کاری و پرداخت فلز و پلاستیک | کارگران رختشویخانه و خشکشویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | قالب‌گیران، شکل‌دهندگان و ریخته‌گران به جز فلز و پلاستیک | نقاشان ساختمان و نگهداری | الگو‌سازان فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آبکاری فلز و پلاستیک | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌های کفش‌دوزی | اپراتورها و متصدیان ماشین‌های رنگرزی و سفیدگری منسوجات | تیزکنندگان و سنگ‌زنان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری به جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | حکاکان و تیزاب‌کاران | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | کارکنان خشک‌شویی و لباس‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | نقاشان، ساختمان و نگهداری | الگوسازان فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>نرم‌افزار کنترل موجودی | سیستم‌های مدیریت موجودی | نرم‌افزار مدیریت نگهداری و تعمیرات | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار رباتیک نقاشی | نرم‌افزار برنامه‌ریزی | نرم‌افزار ثبت زمان</t>
+          <t>نرم‌افزار کنترل موجودی | سیستم‌های مدیریت موجودی | نرم‌افزار مدیریت تعمیر و نگهداری | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار رباتیک نقاشی | نرم‌افزار زمان‌بندی | نرم‌افزار ثبت زمان</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>مانیتورینگ</t>
+          <t>نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | شیمی | مکانیک | زبان انگلیسی | ریاضیات | امنیت و ایمنی عمومی | مهندسی و فناوری</t>
+          <t>تولید و فرآوری | شیمی | مکانیک | زبان انگلیسی | ریاضیات | ایمنی و امنیت عمومی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات دست و بازو | دقت کنترل | تشخیص رنگ بصری | چالاکی دست | چالاکی انگشتان | بینایی دور | قدرت تنه | تجسم فضایی | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی به اطلاعات | استدلال قیاسی | حساسیت به مسئله | درک شفاهی | انعطاف‌پذیری گسترده | قدرت پویا | هماهنگی چند عضو | توجه انتخابی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | دقت کنترل | تشخیص رنگ بصری | مهارت دستی | مهارت انگشتان | بینایی دور | قدرت تنه | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | درک شفاهی | انعطاف‌پذیری دامنه حرکت | قدرت پویا | هماهنگی چند عضو | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوحی از نویز که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای انجام حرکات تکراری | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | صرف زمان به صورت ایستاده | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | اهمیت دقیق یا درست بودن | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا حفاظت در برابر تشعشع | صرف زمان برای راه رفتن یا دویدن | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض شرایط خطرناک | ارتباط با دیگران</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای انجام حرکات تکراری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | صرف زمان برای راه رفتن یا دویدن | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض شرایط خطرناک | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تعمیرکاران بدنه خودرو و موارد مرتبط | تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، فرم‌دهی، پرس و متراکم‌سازی | لمینت‌کاران و سازندگان فایبرگلاس | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و صیقل‌کاری دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، صیقل‌کاری و پرداخت فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | کارگران رختشویخانه و خشکشویی | کارگران نگهداری و تعمیرات ماشین‌آلات | قالب‌گیران، شکل‌دهندگان و ریخته‌گران به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | نقاشان ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزیین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آبکاری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های رنگرزی و سفیدگری منسوجات | سازندگان تایر</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تعمیرکنندگان بدنه خودرو و موارد مرتبط | تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | لمینت‌کاران و سازندگان فایبرگلاس | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | کارکنان خشک‌شویی و لباس‌شویی | کارگران تعمیر و نگهداری ماشین‌آلات | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | نقاشان، ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزیین | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | تایر سازان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب خواندن | گوش دادن فعال | مانیتورینگ</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | زبان انگلیسی | امنیت و ایمنی عمومی | کامپیوتر و الکترونیک | آموزش و پرورش | شیمی</t>
+          <t>تولید و فرآوری | زبان انگلیسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | آموزش و پرورش | شیمی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | درک مطلب کتبی | ثبات دست و بازو | درک شفاهی | استدلال استقرایی | چالاکی انگشتان | دقت کنترل | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | هماهنگی چند عضو | چالاکی دست | ترتیب‌دهی به اطلاعات | تجسم فضایی | سرعت ادراکی</t>
+          <t>بینایی نزدیک | درک کتبی | ثبات دست و بازو | درک شفاهی | استدلال استقرایی | مهارت انگشتان | دقت کنترل | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | هماهنگی چند عضو | مهارت دستی | ترتیب‌دهی اطلاعات | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>داخل ساختمان، محیط کنترل‌شده | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض آلاینده‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | پیامد خطا | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | اهمیت تکرار وظایف یکسان | سلامت و ایمنی سایر کارگران | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوحی از نویز که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان به صورت ایستاده</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض آلاینده‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | پیامد خطا | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | اهمیت تکرار وظایف یکسان | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای ایستادن</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | فن‌آوران و تکنسین‌های کالیبراسیون | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای سیستم و پالایشگاه شیمیایی | اپراتورهای ابزار کنترل عددی کامپیوتری | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکنندگان تجهیزات الکترومکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و فرم‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان, اپراتورها و متصدیان ماشین‌های اکسترود، فرم‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | مهندسان میکروسیستم‌ها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تکنسین‌های آزمایشگاه چشم‌پزشکی | تکنسین‌های فوتونیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آبکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری نرم و سخت</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای کارخانه و سامانه‌های شیمیایی | اپراتورهای ابزار کنترل عددی کامپیوتری | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | مهندسان میکروسیستم | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تکنسین‌های آزمایشگاه چشم‌پزشکی | تکنسین‌های فوتونیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | نرم‌افزار Amazon Web Services AWS | Camera Bits Photo Mechanic | صفحات استایل آبشاری CSS | Docker | ExpressDigital Labtricity | Git | HeliconSoft Helicon Focus | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | MongoDB | MySQL | Phase One Capture One | RESTful API | نرم‌افزار SAP | زبان پرس‌و‌جوی ساختاریافته SQL | TypeScript</t>
+          <t>نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | نرم‌افزار Amazon Web Services AWS | Camera Bits Photo Mechanic | برگه‌های سبک آبشاری CSS | Docker | ExpressDigital Labtricity | Git | HeliconSoft Helicon Focus | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | MongoDB | MySQL | Phase One Capture One | RESTful API | نرم‌افزار SAP | زبان پرس‌وجوی ساختاریافته SQL | TypeScript</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب خواندن | تفکر انتقادی | مانیتورینگ</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | کامپیوتر و الکترونیک | تولید و فرآوری | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | رایانه و الکترونیک | تولید و فرآوری | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | تشخیص رنگ بصری | درک شفاهی | بیان شفاهی | درک مطلب کتبی | استدلال قیاسی | ترتیب‌دهی به اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | ثبات دست و بازو | دقت کنترل | وضوح گفتار | چالاکی دست | تجسم فضایی | سرعت ادراکی | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | تشخیص گفتار | چالاکی انگشتان | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بینایی نزدیک | تشخیص رنگ بصری | درک شفاهی | بیان شفاهی | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | ثبات دست و بازو | دقت کنترل | وضوح گفتار | مهارت دستی | تجسم | سرعت ادراکی | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | تشخیص گفتار | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | داخل ساختمان، محیط کنترل‌شده | سروکار داشتن با مشتریان خارجی یا عموم مردم | فشار زمانی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | فن‌آوران و تکنسین‌های کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | تعمیرکاران کامپیوتر، خودپرداز و ماشین‌های اداری | حکاکان و قلم‌زنان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و فرم‌دهی الیاف مصنوعی و شیشه‌ای | بازرسان، ارزیابان، دسته‌بندها، نمونه‌بردارها و توزین‌کنندگان | آپاراتچی‌های سینما | اپراتورهای ماشین‌های اداری به جز کامپیوتر | کارگران نقاشی، پوشش‌دهی و تزیین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | الگو‌سازان فلز و پلاستیک | عکاسان | تکنسین‌های فوتونیک | تکنسین‌ها و کارگران پیش از چاپ | کارگران صحافی و فینیشینگ چاپ | اپراتورهای ماشین چاپ | تکنسین‌های فرآوری نیمه‌رساناها | اپراتورها و متصدیان ماشین‌های رنگرزی و سفیدگری منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | تعمیرکاران کامپیوتر، عابربانک و ماشین‌های اداری | حکاکان و تیزاب‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | آپاراتچی‌های سینما | اپراتورهای ماشین‌های اداری، به جز رایانه | کارگران نقاشی، پوشش‌دهی و تزیین | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | الگوسازان فلز و پلاستیک | عکاسان | تکنسین‌های فوتونیک | تکنسین‌ها و کارگران پیش از چاپ | کارکنان صحافی و پرداخت چاپ | اپراتورهای ماشین چاپ | تکنسین‌های فرآوری نیمه‌رساناها | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1CadCam Unigraphics | Autodesk AutoCAD | BobCAD-CAM | CGTech Vericut CNC | CNC Consulting Machinists' Calculator | CNC Mastercam | Cadem CAPSMill | Cadem CAPSTurn | Cadem NCnet | Cadem seeNC Mill | DP Technology ESPRIT | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Delcam PowerMILL | نرم‌افزار کنترل عددی کامپیوتری مستقیم CNC | نرم‌افزار ERP | EZ-CAM | EditCNC | Eko | ExtraTech Machine Tools Suite | FaceTime | FlashCut CNC | G-code | HOMAG WoodWOP | IMSI TurboCAD | JETCAM | نرم‌افزار طراحی کابینت KCD | Kentech Kipware M CNC | Kentech Kipware Studio | Kentech Kipware T CNC | Kentech Kipware Trig Kalculator | Kentech Kipware X CNC | Kentech PROTALK | نرم‌افزار کارگاه ماشین‌کاری Kentech | M-code | MDSI OpenCNC | MUMPS M | نرم‌افزار طراحی و ساخت به کمک کامپیوتر Mastercam | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | PTC Creo Parametric | PartMaker SwissCAM | Predator DNC | نرم‌افزار SAP | SigmaTEK SigmaNEST | SmartCAMcnc SmartCAM | نرم‌افزار کنترل سرپرستی و گردآوری داده SCADA | TekSoft CAMWorks | UGS Solid Edge | Vero International VISI-Series | Vero Software Edgecam | Vero Software SURFCAM | Virtual Gibbs CADD/CAM | نرم‌افزار بازرسی کار</t>
+          <t>1CadCam Unigraphics | Autodesk AutoCAD | BobCAD-CAM | CGTech Vericut CNC | ماشین‌حساب ماشین‌کاری CNC Consulting | CNC Mastercam | Cadem CAPSMill | Cadem CAPSTurn | Cadem NCnet | Cadem seeNC Mill | DP Technology ESPRIT | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Delcam PowerMILL | نرم‌افزار کنترل عددی کامپیوتری مستقیم CNC | نرم‌افزار ERP | EZ-CAM | EditCNC | Eko | ExtraTech Machine Tools Suite | FaceTime | FlashCut CNC | G-code | HOMAG WoodWOP | IMSI TurboCAD | JETCAM | نرم‌افزار طراحی کابینت KCD | Kentech Kipware M CNC | Kentech Kipware Studio | Kentech Kipware T CNC | Kentech Kipware Trig Kalculator | Kentech Kipware X CNC | Kentech PROTALK | نرم‌افزار کارگاهی Kentech | M-code | MDSI OpenCNC | MUMPS M | نرم‌افزار طراحی و تولید به کمک کامپیوتر Mastercam | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | PTC Creo Parametric | PartMaker SwissCAM | Predator DNC | نرم‌افزار SAP | SigmaTEK SigmaNEST | SmartCAMcnc SmartCAM | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | TekSoft CAMWorks | UGS Solid Edge | Vero International VISI-Series | Vero Software Edgecam | Vero Software SURFCAM | Virtual Gibbs CADD/CAM | نرم‌افزار بازرسی کار</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | گوش دادن فعال | سخن گفتن</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ریاضیات | تولید و فرآوری | مکانیک | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش | طراحی | امور اداری و مدیریت</t>
+          <t>ریاضیات | تولید و فرآوری | مکانیک | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش | طراحی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | زمان عکس‌العمل | دقت کنترل | حساسیت شنوایی | درک شفاهی | سرعت ادراکی | تجسم فضایی | چالاکی دست | چالاکی انگشتان | توجه شنوایی | قدرت تنه | کنترل نرخ | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | درک مطلب کتبی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | درک عمق | تشخیص رنگ بصری | سرعت بستار | توانایی محاسباتی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | زمان عکس‌العمل | دقت کنترل | حساسیت شنوایی | درک شفاهی | سرعت ادراکی | تجسم | مهارت دستی | مهارت انگشتان | توجه شنیداری | قدرت تنه | کنترل نرخ | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | درک کتبی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | درک عمق | تشخیص رنگ بصری | سرعت بستار | توانایی عددی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>بپوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | صرف زمان به صورت ایستاده | فشار زمانی | قرار گرفتن در معرض صداها و سطوحی از نویز که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | سرعت تعیین‌شده توسط سرعت تجهیزات | تاثیر تصمیمات بر همکاران یا نتایج شرکت | داخل ساختمان، محیط کنترل‌شده | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | سرعت تعیین‌شده توسط سرعت تجهیزات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سوراخ‌کاری و بورینگ فلز و پلاستیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکنندگان تجهیزات الکترومکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، صیقل‌کاری و پرداخت فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراشکاری فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندگانه فلز و پلاستیک | تکنسین‌های رباتیک | تیزکنندگان و سنگ‌زنان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری نرم و سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری به جز اره‌کشی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سوراخ‌کاری و بورینگ، فلز و پلاستیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تکنسین‌های رباتیک | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1CadCam Unigraphics | 3D Systems GibbsCAM | Aptean Made2Manage | Autodesk AutoCAD | Autodesk Fusion 360 | Autodesk PartMaker | Autodesk PowerMill | Autodesk PowerShape | BobCAD-CAM | CGTech Vericut CNC | Celeritive Technologies VoluMill | Cimatron CimatronE | DP Technology ESPRIT | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Delcam FeatureCAM | Delcam PartMaker | Dolphin CAD/CAM | زبان نشانه‌گذاری گسترش‌پذیر XML | FANUC CNC | FaceTime | FastCAM | G-code | GO2cam | GeoPath CAD/CAM System | Geometric Technologies CAMWorks | Gerber Technology CutWorks | GibbsCAM | Hypertherm ProNest | ICAM CAM-POST | Intelitek spectraCAM Milling | Intelitek spectraCAM Turning | Kubotek KeyCreator Machinist | LAB SUM3D | M-code | MachineWorks Ltd. MachineWorks | Manusoft Technologies IMOLD | Mastercam computer-aided design and manufacturing software | MecSoft Corporation RhinoCAM | MecSoft Corporation VisualMILL | MecSoft Corporation VisualTURN | Metalcam Fikus Visualcam | Metalix CAD/CAM System cncKad | Metamation MetaCAM | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Missler Software TopSolid | Open Mind Software hyperMILL | PTC Creo Parametric | نرم‌افزار پس‌پردازشگر | RADAN Radbend | نرم‌افزار SAP | SharpCam Ltd. SharpCam | Siemens NX | Siemens Teamcenter | نرم‌افزار شبیه‌سازی | SmartCAMcnc SmartCAM | SolidCAM CAM software | SolidCAM iMachining | Sprut Technology SprutCAM | نرم‌افزار طراحی به کمک کامپیوتر Tebis | Technos Astra R-Nesting | Technos Astra S-Nesting | Top Systems T-FLEX CAM | Uncamco Ucam | Vero Software ALPHACAM Milling | Vero Software ALPHACAM Turning | Vero Software Edgecam | Vero Software PEPS | Vero Software RADAN | Vero Software SMIRTsoftware | Vero Software SURFCAM | Vero Software VISI | Vero Software WorkNC | Vero Software machining STRATEGIST</t>
+          <t>1CadCam Unigraphics | 3D Systems GibbsCAM | Aptean Made2Manage | Autodesk AutoCAD | Autodesk Fusion 360 | Autodesk PartMaker | Autodesk PowerMill | Autodesk PowerShape | BobCAD-CAM | CGTech Vericut CNC | Celeritive Technologies VoluMill | Cimatron CimatronE | DP Technology ESPRIT | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Delcam FeatureCAM | Delcam PartMaker | Dolphin CAD/CAM | زبان نشانه‌گذاری توسعه‌پذیر XML | FANUC CNC | FaceTime | FastCAM | G-code | GO2cam | GeoPath CAD/CAM System | Geometric Technologies CAMWorks | Gerber Technology CutWorks | GibbsCAM | Hypertherm ProNest | ICAM CAM-POST | Intelitek spectraCAM Milling | Intelitek spectraCAM Turning | Kubotek KeyCreator Machinist | LAB SUM3D | M-code | MachineWorks Ltd. MachineWorks | Manusoft Technologies IMOLD | نرم‌افزار طراحی و تولید به کمک کامپیوتر Mastercam | MecSoft Corporation RhinoCAM | MecSoft Corporation VisualMILL | MecSoft Corporation VisualTURN | Metalcam Fikus Visualcam | Metalix CAD/CAM System cncKad | Metamation MetaCAM | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Missler Software TopSolid | Open Mind Software hyperMILL | PTC Creo Parametric | نرم‌افزار پس‌پردازشگر | RADAN Radbend | نرم‌افزار SAP | SharpCam Ltd. SharpCam | Siemens NX | Siemens Teamcenter | نرم‌افزار شبیه‌سازی | SmartCAMcnc SmartCAM | نرم‌افزار SolidCAM CAM | SolidCAM iMachining | Sprut Technology SprutCAM | نرم‌افزار طراحی به کمک کامپیوتر Tebis | Technos Astra R-Nesting | Technos Astra S-Nesting | Top Systems T-FLEX CAM | Uncamco Ucam | Vero Software ALPHACAM Milling | Vero Software ALPHACAM Turning | Vero Software Edgecam | Vero Software PEPS | Vero Software RADAN | Vero Software SMIRTsoftware | Vero Software SURFCAM | Vero Software VISI | Vero Software WorkNC | Vero Software machining STRATEGIST</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>مانیتورینگ | ریاضیات | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب خواندن</t>
+          <t>نظارت | ریاضیات | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مهندسی و فناوری | ریاضیات | طراحی | کامپیوتر و الکترونیک | زبان انگلیسی | آموزش و پرورش | مکانیک</t>
+          <t>تولید و فرآوری | مهندسی و فناوری | ریاضیات | طراحی | رایانه و الکترونیک | زبان انگلیسی | آموزش و پرورش | مکانیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | سرعت ادراکی | استدلال ریاضی | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | درک مطلب کتبی | درک شفاهی | ثبات دست و بازو | توانایی محاسباتی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دقت کنترل | چالاکی انگشتان</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | سرعت ادراکی | استدلال ریاضی | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | درک کتبی | درک شفاهی | ثبات دست و بازو | توانایی عددی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دقت کنترل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | قرار گرفتن در معرض صداها و سطوحی از نویز که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری | داخل ساختمان، محیط کنترل‌شده | سرعت تعیین‌شده توسط سرعت تجهیزات | کار با یا مشارکت در یک گروه کاری یا تیم</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | سرعت تعیین‌شده توسط سرعت تجهیزات | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>فن‌آوران و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | اپراتورهای ابزار کنترل عددی کامپیوتری | برنامه‌نویسان کامپیوتر | فن‌آوران و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | فن‌آوران و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکنندگان تجهیزات الکترومکانیکی | مونتاژکنندگان موتور و سایر ماشین‌ها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراشکاری فلز و پلاستیک | ماشین‌کاران | نقشه کشان مکانیک | فن‌آوران و تکنسین‌های مهندسی مکانیک | مهندسان مکاترونیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندگانه فلز و پلاستیک | الگو‌سازان فلز و پلاستیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
+          <t>تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | اپراتورهای ابزار کنترل عددی کامپیوتری | برنامه‌نویسان کامپیوتر | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | ماشین‌کاران | نقشه‌کشان مکانیک | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکاترونیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | الگوسازان فلز و پلاستیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | مانیتورینگ | درک مطلب خواندن</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چالاکی دست | قدرت ایستا | ثبات دست و بازو | بینایی نزدیک | قدرت تنه | دقت کنترل | حساسیت به مسئله | کنترل نرخ | چالاکی انگشتان | سرعت ادراکی | هماهنگی چند عضو | زمان عکس‌العمل | انعطاف‌پذیری گسترده | درک شفاهی | استقامت | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | استدلال قیاسی | بیان شفاهی | درک مطلب کتبی | تشخیص گفتار | توجه شنوایی | درک عمق | قدرت پویا | انعطاف‌پذیری بستار | استدلال استقرایی | وضوح گفتار</t>
+          <t>مهارت دستی | قدرت ایستا | ثبات دست و بازو | بینایی نزدیک | قدرت تنه | دقت کنترل | حساسیت به مسئله | کنترل نرخ | مهارت انگشتان | سرعت ادراکی | هماهنگی چند عضو | زمان عکس‌العمل | انعطاف‌پذیری دامنه حرکت | درک شفاهی | استقامت | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان شفاهی | درک کتبی | تشخیص گفتار | توجه شنیداری | درک عمق | قدرت پویا | انعطاف‌پذیری بستار | استدلال استقرایی | وضوح گفتار</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | صرف زمان به صورت ایستاده | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوحی از نویز که حواس‌پرت‌کننده یا آزاردهنده هستند | آزادی در تصمیم‌گیری | فشار زمانی | سرعت تعیین‌شده توسط سرعت تجهیزات | پیامدهای کاری و نتایج سایر کارگران | داخل ساختمان، محیط کنترل‌شده | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض تجهیزات خطرناک | سلامت و ایمنی سایر کارگران | پیامد خطا | صرف زمان برای راه رفتن یا دویدن | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان</t>
+          <t>قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | صرف زمان برای ایستادن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | آزادی در تصمیم‌گیری | فشار زمانی | سرعت تعیین‌شده توسط سرعت تجهیزات | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض تجهیزات خطرناک | سلامت و ایمنی سایر کارکنان | پیامد خطا | صرف زمان برای راه رفتن یا دویدن | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>برش‌کاران و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و فرم‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، فرم‌دهی، پرس و متراکم‌سازی | کارگران سنگ‌زنی و صیقل‌کاری دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، صیقل‌کاری و پرداخت فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | قالب‌گیران، شکل‌دهندگان و ریخته‌گران به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندگانه فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های رنگرزی و سفیدگری منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری به جز اره‌کشی</t>
+          <t>برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب خواندن | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | دقت کنترل | ثبات دست و بازو | سرعت ادراکی | ترتیب‌دهی به اطلاعات | قدرت تنه | هماهنگی چند عضو | چالاکی انگشتان | چالاکی دست | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بینایی نزدیک | دقت کنترل | ثبات دست و بازو | سرعت ادراکی | ترتیب‌دهی اطلاعات | قدرت تنه | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان به صورت ایستاده | قرار گرفتن در معرض صداها و سطوحی از نویز که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای راه رفتن یا دویدن | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای راه رفتن یا دویدن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای سیستم و پالایشگاه شیمیایی | تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، سنگ‌زنی و صیقل‌کاری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، فرم‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان ماشین‌های پخت غذا | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | اپراتورها و متصدیان کوره، تنور، خشک‌کن و دیگ بخار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، صیقل‌کاری و پرداخت فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | کارگران رختشویخانه و خشکشویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کن | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آبکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | اپراتورها و متصدیان ماشین‌های رنگرزی و سفیدگری منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای کارخانه و سامانه‌های شیمیایی | تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | کارکنان خشک‌شویی و لباس‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0093_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0093_fa.xlsx
@@ -513,12 +513,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | ریاضیات | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>تولید و فرآوری | مکانیک | ریاضیات | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | پایداری دست و بازو | چابکی انگشتان | دقت کنترل | چابکی دستی | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | تجسم فضایی | مرتب‌سازی اطلاعات | تشخیص گفتار | تمایز رنگ‌ها | سرعت مچ و انگشتان | زمان واکنش | کنترل نرخ حرکت | سرعت ادراک | انعطاف‌پذیری بستار | طبقه‌بندی منعطف | درک کتبی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت انگشتان | دقت کنترل | مهارت دستی | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات | تشخیص گفتار | تشخیص رنگ بصری | سرعت مچ و انگشتان | زمان عکس‌العمل | کنترل نرخ | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | درک کتبی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تعمیرکاران دوربین و تجهیزات عکاسی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و اسلایس | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | قلم‌زنان و حکاکان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | دمندگان، قالب‌ریزان، خمش‌کاران و پرداخت‌کاران شیشه | کارگران پرداخت و سنگ‌زنی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و سنباده‌زنی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تراشکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه تراش فلز و پلاستیک | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران غیر از فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندکاره فلز و پلاستیک | عینک‌سازان (ساخت و فروش عینک) | تکنسین‌های فوتونیک | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری و برزینگ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های صنایع چوب به‌جز اره‌کشی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تعمیرکاران دوربین و تجهیزات عکاسی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | حکاکان و اسیدکاران | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | دمندگان، قالب‌گیران، خم‌کاران و پرداخت‌کاران شیشه | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | عینک‌سازان (ساخت و فروش عینک) | تکنسین‌های فوتونیک و اپتیک | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی | آموزش و تدریس | زبان انگلیسی | ریاضیات | خدمات مشتریان و خدمات فردی</t>
+          <t>تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی | آموزش و پرورش | زبان انگلیسی | ریاضیات | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | دید نزدیک | دقت کنترل | چابکی دستی | سرعت ادراک | حساسیت به مسئله | بیان شفاهی | درک شفاهی | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری بستار | مرتب‌سازی اطلاعات | قدرت تنه | زمان واکنش | کنترل نرخ حرکت | هماهنگی چنداندامی | چابکی انگشتان | وضوح گفتار | تشخیص گفتار</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | دقت کنترل | مهارت دستی | سرعت ادراکی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | قدرت تنه | زمان عکس‌العمل | کنترل نرخ | هماهنگی چند عضو | مهارت انگشتان | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، پرس و فشرده‌سازی | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و دیگ‌های بخار | کارگران پرداخت و سنگ‌زنی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و سنباده‌زنی فلز و پلاستیک | کارگران تغذیه و تخلیه خطوط تولید و ماشین‌آلات | تعمیرکاران و نگه‌دارندگان ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اختلاط و ترکیب | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران غیر از فلز و پلاستیک | کارگران بسته‌بندی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتراسیون، شفاف‌سازی، ته‌نشینی و تقطیر | اپراتورها و متصدیان ماشین‌های رنگرزی و سفیدگری منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های صنایع چوب به‌جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | کارگران بسته‌بندی دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دید نزدیک | پایداری دست و بازو | تمایز رنگ‌ها | چابکی دستی | چابکی انگشتان | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | تشخیص رنگ بصری | مهارت دستی | مهارت انگشتان | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | برش‌کاران و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و اسلایس | قلم‌زنان و حکاکان | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران و رنگ‌کاران نهایی مبلمان و چوب | کارگران پرداخت و سنگ‌زنی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و سنباده‌زنی فلز و پلاستیک | کارگران خشک‌شویی و لاندری | کارگران تغذیه و تخلیه خطوط تولید و ماشین‌آلات | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران غیر از فلز و پلاستیک | نقاشان و رنگ‌کاران ساختمان و تأسیسات | مدل‌سازان و الگوسازان فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آبکاری فلز و پلاستیک | خیاطان و اپراتورهای چرخ خیاطی صنعتی | اپراتورها و متصدیان ماشین‌های کفاشی و چرم | اپراتورها و متصدیان ماشین‌های رنگرزی و سفیدگری منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های صنایع چوب به‌جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | حکاکان و اسیدکاران | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | نقاشان ساختمان و تاسیسات | الگوسازان فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دید نزدیک | پایداری دست و بازو | دقت کنترل | تمایز رنگ‌ها | چابکی دستی | چابکی انگشتان | دید دور | قدرت تنه | تجسم فضایی | سرعت ادراک | انعطاف‌پذیری بستار | مرتب‌سازی اطلاعات | استدلال قیاسی | حساسیت به مسئله | درک شفاهی | انعطاف‌پذیری بدنی | قدرت بدنی پویا | هماهنگی چنداندامی | توجه انتخابی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | دقت کنترل | تشخیص رنگ بصری | مهارت دستی | مهارت انگشتان | بینایی دور | قدرت تنه | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | درک شفاهی | انعطاف‌پذیری دامنه حرکت | قدرت پویا | هماهنگی چند عضو | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | صافکاران و نقاشان بدنه خودرو | کارگران نظافت و شست‌وشوی وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، پرس و فشرده‌سازی | سازندگان و لمینیت‌کاران قطعات فایبرگلاس | پرداخت‌کاران و رنگ‌کاران نهایی مبلمان و چوب | کارگران پرداخت و سنگ‌زنی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و سنباده‌زنی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | کارگران خشک‌شویی و لاندری | تعمیرکاران و نگه‌دارندگان ماشین‌آلات صنعتی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران غیر از فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | نقاشان و رنگ‌کاران ساختمان و تأسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آبکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های رنگرزی و سفیدگری منسوجات | تایرسازان و مونتاژکاران تایر</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | صافکار و نقاش خودرو | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | لایه‌نشانان و سازندگان فایبرگلاس | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | کارگران خشکشویی و رختشویخانه | کارگران تعمیر و نگهداری ماشین‌آلات | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | سازندگان تایر</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | زبان انگلیسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | آموزش و تدریس | شیمی</t>
+          <t>تولید و فرآوری | زبان انگلیسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | آموزش و پرورش | شیمی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک کتبی | پایداری دست و بازو | درک شفاهی | استدلال استقرایی | چابکی انگشتان | دقت کنترل | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | هماهنگی چنداندامی | چابکی دستی | مرتب‌سازی اطلاعات | تجسم فضایی | سرعت ادراک</t>
+          <t>بینایی نزدیک | درک کتبی | ثبات دست و بازو | درک شفاهی | استدلال استقرایی | مهارت انگشتان | دقت کنترل | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | هماهنگی چند عضو | مهارت دستی | ترتیب‌دهی اطلاعات | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | کارشناسان و تکنسین‌های کالیبراسیون | اپراتورها و متصدیان تجهیزات فرآیندهای شیمیایی | اپراتورهای کارخانه‌ها و سیستم‌های فرآوری شیمیایی | اپراتورهای ماشین‌ابزارهای CNC | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، پرس و فشرده‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | مهندسان میکروسیستم‌ها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه تراش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | تکنسین‌های فوتونیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آبکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتراسیون، شفاف‌سازی، ته‌نشینی و تقطیر | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری و برزینگ</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌ها و کارشناسان فنی کالیبراسیون | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | تکنسین‌های فوتونیک و اپتیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | تولید و فرآوری | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | رایانه و الکترونیک | تولید و فرآوری | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | تمایز رنگ‌ها | درک شفاهی | بیان شفاهی | درک کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | پایداری دست و بازو | دقت کنترل | وضوح گفتار | چابکی دستی | تجسم فضایی | سرعت ادراک | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | تشخیص گفتار | چابکی انگشتان | طبقه‌بندی منعطف</t>
+          <t>بینایی نزدیک | تشخیص رنگ بصری | درک شفاهی | بیان شفاهی | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | ثبات دست و بازو | دقت کنترل | وضوح گفتار | مهارت دستی | تجسم | سرعت ادراکی | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | تشخیص گفتار | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | کارشناسان و تکنسین‌های کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | تعمیرکاران تجهیزات اداری، رایانه‌ای و خودپردازها | قلم‌زنان و حکاکان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | بازرسان، ارزیابان، دسته‌بندی‌کنندگان، نمونه‌برداران و توزین‌کنندگان | آپاراتچی‌ها و متصدیان نمایش فیلم | اپراتورهای ماشین‌آلات اداری به‌جز رایانه | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | مدل‌سازان و الگوسازان فلز و پلاستیک | عکاسان | تکنسین‌های فوتونیک | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | صحافان و کارگران مراحل پایانی چاپ | اپراتورهای ماشین‌های چاپ صنعتی | تکنسین‌های فرآوری و ساخت نیمه‌هادی‌ها | اپراتورها و متصدیان ماشین‌های رنگرزی و سفیدگری منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | حکاکان و اسیدکاران | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | آپاراتچی‌ها و تکنسین‌های نمایش فیلم | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | الگوسازان فلز و پلاستیک | عکاسان | تکنسین‌های فوتونیک و اپتیک | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | کارگران صحافی و تکمیل چاپ | اپراتورهای ماشین‌های چاپ | تکنسین‌های فرآوری و ساخت نیمه‌هادی‌ها | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ریاضیات | تولید و فرآوری | مکانیک | زبان انگلیسی | مهندسی و فناوری | آموزش و تدریس | طراحی | مدیریت و امور اداری</t>
+          <t>ریاضیات | تولید و فرآوری | مکانیک | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش | طراحی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | زمان واکنش | دقت کنترل | حساسیت شنوایی | درک شفاهی | سرعت ادراک | تجسم فضایی | چابکی دستی | چابکی انگشتان | توجه شنوایی | قدرت تنه | کنترل نرخ حرکت | هماهنگی چنداندامی | توجه انتخابی | انعطاف‌پذیری بستار | طبقه‌بندی منعطف | استدلال قیاسی | درک کتبی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | ادراک عمق | تمایز رنگ‌ها | سرعت درک الگوها | توانایی کار با اعداد</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | زمان عکس‌العمل | دقت کنترل | حساسیت شنوایی | درک شفاهی | سرعت ادراکی | تجسم | مهارت دستی | مهارت انگشتان | توجه شنیداری | قدرت تنه | کنترل نرخ | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | درک کتبی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | درک عمق | تشخیص رنگ بصری | سرعت بستار | توانایی عددی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | برنامه‌نویسان ماشین‌ابزارهای CNC | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های حفاری و بورینگ فلز و پلاستیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آهنگری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و سنباده‌زنی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تراشکاری فلز و پلاستیک | تراشکاران و ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه تراش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندکاره فلز و پلاستیک | تکنسین‌های رباتیک صنعتی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری و برزینگ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های صنایع چوب به‌جز اره‌کشی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تکنسین‌های رباتیک | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | ریاضیات | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | ریاضیات | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مهندسی و فناوری | ریاضیات | طراحی | رایانه و الکترونیک | زبان انگلیسی | آموزش و تدریس | مکانیک</t>
+          <t>تولید و فرآوری | مهندسی و فناوری | ریاضیات | طراحی | رایانه و الکترونیک | زبان انگلیسی | آموزش و پرورش | مکانیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | سرعت ادراک | استدلال ریاضی | توجه انتخابی | تجسم فضایی | طبقه‌بندی منعطف | درک کتبی | درک شفاهی | پایداری دست و بازو | توانایی کار با اعداد | استدلال استقرایی | استدلال قیاسی | بیان کتبی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دقت کنترل | چابکی انگشتان</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | سرعت ادراکی | استدلال ریاضی | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | درک کتبی | درک شفاهی | ثبات دست و بازو | توانایی عددی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دقت کنترل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار رایانه | اپراتورهای ماشین‌ابزارهای CNC | برنامه‌نویسان رایانه | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تراشکاری فلز و پلاستیک | تراشکاران و ماشین‌کاران | نقشه‌کشان صنعتی و مکانیک | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکاترونیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه تراش فلز و پلاستیک | مدل‌سازان و الگوسازان فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندکاره فلز و پلاستیک | مدل‌سازان و الگوبرداران فلز و پلاستیک | مهندسان رباتیک | تکنسین‌های رباتیک صنعتی</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان سخت‌افزار رایانه | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | برنامه‌نویسان کامپیوتر | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | نقشه‌کشان مکانیک | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکاترونیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | الگوسازان فلز و پلاستیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی دستی | قدرت ایستایی | پایداری دست و بازو | دید نزدیک | قدرت تنه | دقت کنترل | حساسیت به مسئله | کنترل نرخ حرکت | چابکی انگشتان | سرعت ادراک | هماهنگی چنداندامی | زمان واکنش | انعطاف‌پذیری بدنی | درک شفاهی | استقامت بدنی | توجه انتخابی | تجسم فضایی | طبقه‌بندی منعطف | مرتب‌سازی اطلاعات | استدلال قیاسی | بیان شفاهی | درک کتبی | تشخیص گفتار | توجه شنوایی | ادراک عمق | قدرت بدنی پویا | انعطاف‌پذیری بستار | استدلال استقرایی | وضوح گفتار</t>
+          <t>مهارت دستی | قدرت ایستا | ثبات دست و بازو | بینایی نزدیک | قدرت تنه | دقت کنترل | حساسیت به مسئله | کنترل نرخ | مهارت انگشتان | سرعت ادراکی | هماهنگی چند عضو | زمان عکس‌العمل | انعطاف‌پذیری دامنه حرکت | درک شفاهی | استقامت | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان شفاهی | درک کتبی | تشخیص گفتار | توجه شنیداری | درک عمق | قدرت پویا | انعطاف‌پذیری بستار | استدلال استقرایی | وضوح گفتار</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>برش‌کاران و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، پرس و فشرده‌سازی | کارگران پرداخت و سنگ‌زنی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و سنباده‌زنی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | کارگران تغذیه و تخلیه خطوط تولید و ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه تراش فلز و پلاستیک | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران غیر از فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندکاره فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های رنگرزی و سفیدگری منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های صنایع چوب به‌جز اره‌کشی</t>
+          <t>برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | دقت کنترل | پایداری دست و بازو | سرعت ادراک | مرتب‌سازی اطلاعات | قدرت تنه | هماهنگی چنداندامی | چابکی انگشتان | چابکی دستی | طبقه‌بندی منعطف</t>
+          <t>بینایی نزدیک | دقت کنترل | ثبات دست و بازو | سرعت ادراکی | ترتیب‌دهی اطلاعات | قدرت تنه | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | اپراتورها و متصدیان تجهیزات فرآیندهای شیمیایی | اپراتورهای کارخانه‌ها و سیستم‌های فرآوری شیمیایی | کارگران نظافت و شست‌وشوی وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، پرس و فشرده‌سازی | اپراتورها و متصدیان ماشین‌های پخت و فرآوری مواد غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و توتون | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و دیگ‌های بخار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و سنباده‌زنی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | کارگران خشک‌شویی و لاندری | کارگران تغذیه و تخلیه خطوط تولید و ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اختلاط و ترکیب | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آبکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتراسیون، شفاف‌سازی، ته‌نشینی و تقطیر | اپراتورها و متصدیان ماشین‌های رنگرزی و سفیدگری منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | اپراتورهای ماشین‌آلات پخت مواد غذایی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
